--- a/基礎演習/Java基礎⑦_クラスの応用_演習問題.xlsx
+++ b/基礎演習/Java基礎⑦_クラスの応用_演習問題.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\村石 莉彩\Desktop\研修資料\10_Java\02_演習\01_基礎\問題\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120\workspace\Java\基礎演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FD8090-EA31-40DA-A663-4566A6F27140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47A67C2-C22A-4E42-A97D-27FB9B8C4EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-6570" windowWidth="14610" windowHeight="15585" tabRatio="827" firstSheet="4" activeTab="5" xr2:uid="{1C3E7292-E396-45A8-B2DC-610351FF3847}"/>
+    <workbookView xWindow="28695" yWindow="-6570" windowWidth="14610" windowHeight="15585" tabRatio="827" firstSheet="4" activeTab="6" xr2:uid="{1C3E7292-E396-45A8-B2DC-610351FF3847}"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="10" r:id="rId1"/>
@@ -1562,6 +1562,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100D00E93C39DF401468E770D4882DF02E4" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="96f527420be350019f68a523211badd0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4f770298-b31c-4238-a90d-db1340869ae4" xmlns:ns3="4ebca473-6c88-4eeb-9b46-7f2093239612" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43e7199c2f8c1b8a43238954ae45261b" ns2:_="" ns3:_="">
     <xsd:import namespace="4f770298-b31c-4238-a90d-db1340869ae4"/>
@@ -1768,27 +1788,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A3ABA9F-9534-456D-B4A8-5DEF58BD928B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3B316C2-B42E-42D6-A043-0E763112260A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
+    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ABF6128-32C3-4C8A-9924-8B62ED77E703}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1805,29 +1830,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3B316C2-B42E-42D6-A043-0E763112260A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
-    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A3ABA9F-9534-456D-B4A8-5DEF58BD928B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>